--- a/data/KYN_KJT/upse_signals.xlsx
+++ b/data/KYN_KJT/upse_signals.xlsx
@@ -546,6 +546,12 @@
       <c r="W2">
         <v>1</v>
       </c>
+      <c r="X2" t="str">
+        <v/>
+      </c>
+      <c r="Y2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -569,6 +575,9 @@
       <c r="G3" t="str">
         <v>PF-2 STR</v>
       </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
       <c r="I3" t="str">
         <v>Manual</v>
       </c>
@@ -613,6 +622,12 @@
       </c>
       <c r="W3">
         <v>1</v>
+      </c>
+      <c r="X3" t="str">
+        <v/>
+      </c>
+      <c r="Y3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -637,6 +652,9 @@
       <c r="G4" t="str">
         <v>PF-3 STR</v>
       </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
       <c r="I4" t="str">
         <v>Manual</v>
       </c>
@@ -681,6 +699,12 @@
       </c>
       <c r="W4">
         <v>1</v>
+      </c>
+      <c r="X4" t="str">
+        <v/>
+      </c>
+      <c r="Y4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -705,6 +729,9 @@
       <c r="G5" t="str">
         <v>EMU PF STR</v>
       </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
       <c r="I5" t="str">
         <v>Manual</v>
       </c>
@@ -749,6 +776,12 @@
       </c>
       <c r="W5">
         <v>1</v>
+      </c>
+      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -773,6 +806,9 @@
       <c r="G6" t="str">
         <v>UP ML</v>
       </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
       <c r="I6" t="str">
         <v>Manual</v>
       </c>
@@ -817,6 +853,12 @@
       </c>
       <c r="W6">
         <v>1</v>
+      </c>
+      <c r="X6" t="str">
+        <v/>
+      </c>
+      <c r="Y6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -880,17 +922,32 @@
       <c r="T7">
         <v>0</v>
       </c>
+      <c r="U7" t="str">
+        <v/>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
       <c r="W7">
         <v>1</v>
       </c>
       <c r="X7" t="str">
         <v>98/27</v>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>Gate-27</v>
       </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
       <c r="D8" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -941,6 +998,12 @@
       </c>
       <c r="T8">
         <v>0</v>
+      </c>
+      <c r="U8" t="str">
+        <v/>
+      </c>
+      <c r="V8" t="str">
+        <v/>
       </c>
       <c r="W8">
         <v>1</v>
@@ -956,6 +1019,12 @@
       <c r="A9" t="str">
         <v>SE-9706</v>
       </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
       <c r="D9" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -1006,6 +1075,12 @@
       </c>
       <c r="T9">
         <v>0</v>
+      </c>
+      <c r="U9" t="str">
+        <v/>
+      </c>
+      <c r="V9" t="str">
+        <v/>
       </c>
       <c r="W9">
         <v>1</v>
@@ -1021,6 +1096,12 @@
       <c r="A10" t="str">
         <v>Gate-26</v>
       </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
       <c r="D10" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -1071,6 +1152,12 @@
       </c>
       <c r="T10">
         <v>0</v>
+      </c>
+      <c r="U10" t="str">
+        <v/>
+      </c>
+      <c r="V10" t="str">
+        <v/>
       </c>
       <c r="W10">
         <v>1</v>
@@ -1086,6 +1173,12 @@
       <c r="A11" t="str">
         <v>SE-9602</v>
       </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
       <c r="D11" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -1136,6 +1229,12 @@
       </c>
       <c r="T11">
         <v>0</v>
+      </c>
+      <c r="U11" t="str">
+        <v/>
+      </c>
+      <c r="V11" t="str">
+        <v/>
       </c>
       <c r="W11">
         <v>1</v>
@@ -1151,6 +1250,12 @@
       <c r="A12" t="str">
         <v>Gate-25</v>
       </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
       <c r="D12" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -1201,6 +1306,12 @@
       </c>
       <c r="T12">
         <v>0</v>
+      </c>
+      <c r="U12" t="str">
+        <v/>
+      </c>
+      <c r="V12" t="str">
+        <v/>
       </c>
       <c r="W12">
         <v>1</v>
@@ -1216,6 +1327,12 @@
       <c r="A13" t="str">
         <v>SE-9410</v>
       </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
       <c r="D13" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -1266,6 +1383,12 @@
       </c>
       <c r="T13">
         <v>0</v>
+      </c>
+      <c r="U13" t="str">
+        <v/>
+      </c>
+      <c r="V13" t="str">
+        <v/>
       </c>
       <c r="W13">
         <v>1</v>
@@ -1415,8 +1538,17 @@
       <c r="T15">
         <v>0</v>
       </c>
+      <c r="U15" t="str">
+        <v/>
+      </c>
+      <c r="V15" t="str">
+        <v/>
+      </c>
       <c r="W15">
         <v>1</v>
+      </c>
+      <c r="X15" t="str">
+        <v/>
       </c>
       <c r="Y15">
         <v>1200</v>
@@ -1483,6 +1615,12 @@
       <c r="T16">
         <v>0</v>
       </c>
+      <c r="U16" t="str">
+        <v/>
+      </c>
+      <c r="V16" t="str">
+        <v/>
+      </c>
       <c r="W16">
         <v>1</v>
       </c>
@@ -1497,6 +1635,12 @@
       <c r="A17" t="str">
         <v>SE-9012</v>
       </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
       <c r="D17" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -1547,6 +1691,12 @@
       </c>
       <c r="T17">
         <v>0</v>
+      </c>
+      <c r="U17" t="str">
+        <v/>
+      </c>
+      <c r="V17" t="str">
+        <v/>
       </c>
       <c r="W17">
         <v>1</v>
@@ -1562,6 +1712,12 @@
       <c r="A18" t="str">
         <v>Gate-22 S-3</v>
       </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
       <c r="D18" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -1612,6 +1768,12 @@
       </c>
       <c r="T18">
         <v>0</v>
+      </c>
+      <c r="U18" t="str">
+        <v/>
+      </c>
+      <c r="V18" t="str">
+        <v/>
       </c>
       <c r="W18">
         <v>1</v>
@@ -1627,6 +1789,12 @@
       <c r="A19" t="str">
         <v>SE-8906</v>
       </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
       <c r="D19" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -1677,6 +1845,12 @@
       </c>
       <c r="T19">
         <v>0</v>
+      </c>
+      <c r="U19" t="str">
+        <v/>
+      </c>
+      <c r="V19" t="str">
+        <v/>
       </c>
       <c r="W19">
         <v>1</v>
@@ -1692,6 +1866,12 @@
       <c r="A20" t="str">
         <v>SE-8808</v>
       </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
       <c r="D20" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -1742,6 +1922,12 @@
       </c>
       <c r="T20">
         <v>0</v>
+      </c>
+      <c r="U20" t="str">
+        <v/>
+      </c>
+      <c r="V20" t="str">
+        <v/>
       </c>
       <c r="W20">
         <v>1</v>
@@ -1757,6 +1943,12 @@
       <c r="A21" t="str">
         <v>SE-8710</v>
       </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
       <c r="D21" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -1807,6 +1999,12 @@
       </c>
       <c r="T21">
         <v>0</v>
+      </c>
+      <c r="U21" t="str">
+        <v/>
+      </c>
+      <c r="V21" t="str">
+        <v/>
       </c>
       <c r="W21">
         <v>1</v>
@@ -1879,6 +2077,12 @@
       <c r="T22">
         <v>0</v>
       </c>
+      <c r="U22" t="str">
+        <v/>
+      </c>
+      <c r="V22" t="str">
+        <v/>
+      </c>
       <c r="W22">
         <v>1</v>
       </c>
@@ -1959,6 +2163,9 @@
       <c r="W23">
         <v>1</v>
       </c>
+      <c r="X23" t="str">
+        <v/>
+      </c>
       <c r="Y23">
         <v>700</v>
       </c>
@@ -2024,6 +2231,12 @@
       <c r="T24">
         <v>0</v>
       </c>
+      <c r="U24" t="str">
+        <v/>
+      </c>
+      <c r="V24" t="str">
+        <v/>
+      </c>
       <c r="W24">
         <v>1</v>
       </c>
@@ -2038,6 +2251,12 @@
       <c r="A25" t="str">
         <v>Gate-20</v>
       </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
       <c r="D25" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -2088,6 +2307,12 @@
       </c>
       <c r="T25">
         <v>0</v>
+      </c>
+      <c r="U25" t="str">
+        <v/>
+      </c>
+      <c r="V25" t="str">
+        <v/>
       </c>
       <c r="W25">
         <v>1</v>
@@ -2103,6 +2328,12 @@
       <c r="A26" t="str">
         <v>SE-8308</v>
       </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
       <c r="D26" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -2153,6 +2384,12 @@
       </c>
       <c r="T26">
         <v>0</v>
+      </c>
+      <c r="U26" t="str">
+        <v/>
+      </c>
+      <c r="V26" t="str">
+        <v/>
       </c>
       <c r="W26">
         <v>1</v>
@@ -2168,6 +2405,12 @@
       <c r="A27" t="str">
         <v>SE-8214</v>
       </c>
+      <c r="B27" t="str">
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
       <c r="D27" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -2218,6 +2461,12 @@
       </c>
       <c r="T27">
         <v>0</v>
+      </c>
+      <c r="U27" t="str">
+        <v/>
+      </c>
+      <c r="V27" t="str">
+        <v/>
       </c>
       <c r="W27">
         <v>1</v>
@@ -2233,6 +2482,12 @@
       <c r="A28" t="str">
         <v>SE-8206</v>
       </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
       <c r="D28" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -2283,6 +2538,12 @@
       </c>
       <c r="T28">
         <v>0</v>
+      </c>
+      <c r="U28" t="str">
+        <v/>
+      </c>
+      <c r="V28" t="str">
+        <v/>
       </c>
       <c r="W28">
         <v>1</v>
@@ -2298,6 +2559,12 @@
       <c r="A29" t="str">
         <v>Gate-19 S-3</v>
       </c>
+      <c r="B29" t="str">
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
       <c r="D29" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -2348,6 +2615,12 @@
       </c>
       <c r="T29">
         <v>0</v>
+      </c>
+      <c r="U29" t="str">
+        <v/>
+      </c>
+      <c r="V29" t="str">
+        <v/>
       </c>
       <c r="W29">
         <v>1</v>
@@ -2363,6 +2636,12 @@
       <c r="A30" t="str">
         <v>SE-8014</v>
       </c>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
       <c r="D30" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -2413,6 +2692,12 @@
       </c>
       <c r="T30">
         <v>0</v>
+      </c>
+      <c r="U30" t="str">
+        <v/>
+      </c>
+      <c r="V30" t="str">
+        <v/>
       </c>
       <c r="W30">
         <v>1</v>
@@ -2428,6 +2713,12 @@
       <c r="A31" t="str">
         <v>Gate-18</v>
       </c>
+      <c r="B31" t="str">
+        <v/>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
       <c r="D31" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -2478,6 +2769,12 @@
       </c>
       <c r="T31">
         <v>0</v>
+      </c>
+      <c r="U31" t="str">
+        <v/>
+      </c>
+      <c r="V31" t="str">
+        <v/>
       </c>
       <c r="W31">
         <v>1</v>
@@ -2493,6 +2790,12 @@
       <c r="A32" t="str">
         <v>SE-7912</v>
       </c>
+      <c r="B32" t="str">
+        <v/>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
       <c r="D32" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -2543,6 +2846,12 @@
       </c>
       <c r="T32">
         <v>0</v>
+      </c>
+      <c r="U32" t="str">
+        <v/>
+      </c>
+      <c r="V32" t="str">
+        <v/>
       </c>
       <c r="W32">
         <v>1</v>
@@ -2692,8 +3001,17 @@
       <c r="T34">
         <v>0</v>
       </c>
+      <c r="U34" t="str">
+        <v/>
+      </c>
+      <c r="V34" t="str">
+        <v/>
+      </c>
       <c r="W34">
         <v>1</v>
+      </c>
+      <c r="X34" t="str">
+        <v/>
       </c>
       <c r="Y34">
         <v>350</v>
@@ -2760,6 +3078,12 @@
       <c r="T35">
         <v>0</v>
       </c>
+      <c r="U35" t="str">
+        <v/>
+      </c>
+      <c r="V35" t="str">
+        <v/>
+      </c>
       <c r="W35">
         <v>1</v>
       </c>
@@ -2774,6 +3098,12 @@
       <c r="A36" t="str">
         <v>Gate-16</v>
       </c>
+      <c r="B36" t="str">
+        <v/>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
       <c r="D36" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -2824,6 +3154,12 @@
       </c>
       <c r="T36">
         <v>0</v>
+      </c>
+      <c r="U36" t="str">
+        <v/>
+      </c>
+      <c r="V36" t="str">
+        <v/>
       </c>
       <c r="W36">
         <v>1</v>
@@ -2839,6 +3175,12 @@
       <c r="A37" t="str">
         <v>SE-7514</v>
       </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
       <c r="D37" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -2889,6 +3231,12 @@
       </c>
       <c r="T37">
         <v>0</v>
+      </c>
+      <c r="U37" t="str">
+        <v/>
+      </c>
+      <c r="V37" t="str">
+        <v/>
       </c>
       <c r="W37">
         <v>1</v>
@@ -2904,6 +3252,12 @@
       <c r="A38" t="str">
         <v>SE-7504</v>
       </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
       <c r="D38" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -2954,6 +3308,12 @@
       </c>
       <c r="T38">
         <v>0</v>
+      </c>
+      <c r="U38" t="str">
+        <v/>
+      </c>
+      <c r="V38" t="str">
+        <v/>
       </c>
       <c r="W38">
         <v>1</v>
@@ -2969,6 +3329,12 @@
       <c r="A39" t="str">
         <v>SE-7406</v>
       </c>
+      <c r="B39" t="str">
+        <v/>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
       <c r="D39" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -3019,6 +3385,12 @@
       </c>
       <c r="T39">
         <v>0</v>
+      </c>
+      <c r="U39" t="str">
+        <v/>
+      </c>
+      <c r="V39" t="str">
+        <v/>
       </c>
       <c r="W39">
         <v>1</v>
@@ -3034,6 +3406,12 @@
       <c r="A40" t="str">
         <v>SE-7308</v>
       </c>
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
       <c r="D40" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -3084,6 +3462,12 @@
       </c>
       <c r="T40">
         <v>0</v>
+      </c>
+      <c r="U40" t="str">
+        <v/>
+      </c>
+      <c r="V40" t="str">
+        <v/>
       </c>
       <c r="W40">
         <v>1</v>
@@ -3099,6 +3483,12 @@
       <c r="A41" t="str">
         <v>SE-7220</v>
       </c>
+      <c r="B41" t="str">
+        <v/>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
       <c r="D41" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -3149,6 +3539,12 @@
       </c>
       <c r="T41">
         <v>0</v>
+      </c>
+      <c r="U41" t="str">
+        <v/>
+      </c>
+      <c r="V41" t="str">
+        <v/>
       </c>
       <c r="W41">
         <v>1</v>
@@ -3164,6 +3560,12 @@
       <c r="A42" t="str">
         <v>SE-7114</v>
       </c>
+      <c r="B42" t="str">
+        <v/>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
       <c r="D42" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -3214,6 +3616,12 @@
       </c>
       <c r="T42">
         <v>0</v>
+      </c>
+      <c r="U42" t="str">
+        <v/>
+      </c>
+      <c r="V42" t="str">
+        <v/>
       </c>
       <c r="W42">
         <v>1</v>
@@ -3229,6 +3637,12 @@
       <c r="A43" t="str">
         <v>SE-7014</v>
       </c>
+      <c r="B43" t="str">
+        <v/>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
       <c r="D43" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -3279,6 +3693,12 @@
       </c>
       <c r="T43">
         <v>0</v>
+      </c>
+      <c r="U43" t="str">
+        <v/>
+      </c>
+      <c r="V43" t="str">
+        <v/>
       </c>
       <c r="W43">
         <v>1</v>
@@ -3294,6 +3714,12 @@
       <c r="A44" t="str">
         <v>SE-6914</v>
       </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
       <c r="D44" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -3344,6 +3770,12 @@
       </c>
       <c r="T44">
         <v>0</v>
+      </c>
+      <c r="U44" t="str">
+        <v/>
+      </c>
+      <c r="V44" t="str">
+        <v/>
       </c>
       <c r="W44">
         <v>1</v>
@@ -3416,6 +3848,12 @@
       <c r="T45">
         <v>0</v>
       </c>
+      <c r="U45" t="str">
+        <v/>
+      </c>
+      <c r="V45" t="str">
+        <v/>
+      </c>
       <c r="W45">
         <v>1</v>
       </c>
@@ -3487,6 +3925,12 @@
       <c r="T46">
         <v>0</v>
       </c>
+      <c r="U46" t="str">
+        <v/>
+      </c>
+      <c r="V46" t="str">
+        <v/>
+      </c>
       <c r="W46">
         <v>1</v>
       </c>
@@ -3558,8 +4002,17 @@
       <c r="T47">
         <v>0</v>
       </c>
+      <c r="U47" t="str">
+        <v/>
+      </c>
+      <c r="V47" t="str">
+        <v/>
+      </c>
       <c r="W47">
         <v>1</v>
+      </c>
+      <c r="X47" t="str">
+        <v/>
       </c>
       <c r="Y47">
         <v>450</v>
@@ -3626,6 +4079,12 @@
       <c r="T48">
         <v>0</v>
       </c>
+      <c r="U48" t="str">
+        <v/>
+      </c>
+      <c r="V48" t="str">
+        <v/>
+      </c>
       <c r="W48">
         <v>1</v>
       </c>
@@ -3640,6 +4099,12 @@
       <c r="A49" t="str">
         <v>SE-6526</v>
       </c>
+      <c r="B49" t="str">
+        <v/>
+      </c>
+      <c r="C49" t="str">
+        <v/>
+      </c>
       <c r="D49" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -3690,6 +4155,12 @@
       </c>
       <c r="T49">
         <v>0</v>
+      </c>
+      <c r="U49" t="str">
+        <v/>
+      </c>
+      <c r="V49" t="str">
+        <v/>
       </c>
       <c r="W49">
         <v>1</v>
@@ -3705,6 +4176,12 @@
       <c r="A50" t="str">
         <v>SE-6410</v>
       </c>
+      <c r="B50" t="str">
+        <v/>
+      </c>
+      <c r="C50" t="str">
+        <v/>
+      </c>
       <c r="D50" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -3755,6 +4232,12 @@
       </c>
       <c r="T50">
         <v>0</v>
+      </c>
+      <c r="U50" t="str">
+        <v/>
+      </c>
+      <c r="V50" t="str">
+        <v/>
       </c>
       <c r="W50">
         <v>1</v>
@@ -3770,6 +4253,12 @@
       <c r="A51" t="str">
         <v>Gate-7</v>
       </c>
+      <c r="B51" t="str">
+        <v/>
+      </c>
+      <c r="C51" t="str">
+        <v/>
+      </c>
       <c r="D51" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -3820,6 +4309,12 @@
       </c>
       <c r="T51">
         <v>0</v>
+      </c>
+      <c r="U51" t="str">
+        <v/>
+      </c>
+      <c r="V51" t="str">
+        <v/>
       </c>
       <c r="W51">
         <v>1</v>
@@ -3835,6 +4330,12 @@
       <c r="A52" t="str">
         <v>SE-6214</v>
       </c>
+      <c r="B52" t="str">
+        <v/>
+      </c>
+      <c r="C52" t="str">
+        <v/>
+      </c>
       <c r="D52" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -3885,6 +4386,12 @@
       </c>
       <c r="T52">
         <v>0</v>
+      </c>
+      <c r="U52" t="str">
+        <v/>
+      </c>
+      <c r="V52" t="str">
+        <v/>
       </c>
       <c r="W52">
         <v>1</v>
@@ -3900,6 +4407,12 @@
       <c r="A53" t="str">
         <v>SE-6202</v>
       </c>
+      <c r="B53" t="str">
+        <v/>
+      </c>
+      <c r="C53" t="str">
+        <v/>
+      </c>
       <c r="D53" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -3951,11 +4464,20 @@
       <c r="T53">
         <v>0</v>
       </c>
+      <c r="U53" t="str">
+        <v/>
+      </c>
+      <c r="V53" t="str">
+        <v/>
+      </c>
       <c r="W53">
         <v>1</v>
       </c>
       <c r="X53" t="str">
         <v>62/05</v>
+      </c>
+      <c r="Y53" t="str">
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -4173,8 +4695,17 @@
       <c r="T56">
         <v>0</v>
       </c>
+      <c r="U56" t="str">
+        <v/>
+      </c>
+      <c r="V56" t="str">
+        <v/>
+      </c>
       <c r="W56">
         <v>1</v>
+      </c>
+      <c r="X56" t="str">
+        <v/>
       </c>
       <c r="Y56">
         <v>400</v>
@@ -4184,6 +4715,12 @@
       <c r="A57" t="str">
         <v xml:space="preserve">Gate-4 </v>
       </c>
+      <c r="B57" t="str">
+        <v/>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
       <c r="D57" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -4234,6 +4771,12 @@
       </c>
       <c r="T57">
         <v>0</v>
+      </c>
+      <c r="U57" t="str">
+        <v/>
+      </c>
+      <c r="V57" t="str">
+        <v/>
       </c>
       <c r="W57">
         <v>1</v>
@@ -4249,6 +4792,12 @@
       <c r="A58" t="str">
         <v>SE-5714</v>
       </c>
+      <c r="B58" t="str">
+        <v/>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
       <c r="D58" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -4299,6 +4848,12 @@
       </c>
       <c r="T58">
         <v>0</v>
+      </c>
+      <c r="U58" t="str">
+        <v/>
+      </c>
+      <c r="V58" t="str">
+        <v/>
       </c>
       <c r="W58">
         <v>1</v>
@@ -4314,6 +4869,12 @@
       <c r="A59" t="str">
         <v>SE-5616</v>
       </c>
+      <c r="B59" t="str">
+        <v/>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
       <c r="D59" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -4365,8 +4926,17 @@
       <c r="T59">
         <v>0</v>
       </c>
+      <c r="U59" t="str">
+        <v/>
+      </c>
+      <c r="V59" t="str">
+        <v/>
+      </c>
       <c r="W59">
         <v>1</v>
+      </c>
+      <c r="X59" t="str">
+        <v/>
       </c>
       <c r="Y59">
         <v>300</v>
@@ -4376,6 +4946,12 @@
       <c r="A60" t="str">
         <v>SE-5602</v>
       </c>
+      <c r="B60" t="str">
+        <v/>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
       <c r="D60" t="str">
         <v>KYN-KJT</v>
       </c>
@@ -4426,6 +5002,12 @@
       </c>
       <c r="T60">
         <v>0</v>
+      </c>
+      <c r="U60" t="str">
+        <v/>
+      </c>
+      <c r="V60" t="str">
+        <v/>
       </c>
       <c r="W60">
         <v>1</v>
@@ -4463,7 +5045,7 @@
         <v>54.754999999999995</v>
       </c>
       <c r="I61" t="str">
-        <v>Manual</v>
+        <v>Semi-Automatic</v>
       </c>
       <c r="J61" t="str">
         <v>Left</v>
@@ -4540,7 +5122,7 @@
         <v>53.765</v>
       </c>
       <c r="I62" t="str">
-        <v>Manual</v>
+        <v>Semi-Automatic</v>
       </c>
       <c r="J62" t="str">
         <v>Left</v>
